--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487639_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487639_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.5229</v>
+        <v>2.796</v>
       </c>
       <c r="E2" t="n">
-        <v>4.5348</v>
+        <v>4.8351</v>
       </c>
       <c r="F2" t="n">
-        <v>-2.0119</v>
+        <v>-2.0391</v>
       </c>
       <c r="G2" t="n">
         <v>-0.4342</v>
@@ -610,13 +610,13 @@
         <v>1.1642</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.0428</v>
+        <v>0.2302</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.3993</v>
+        <v>-0.099</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3565</v>
+        <v>0.3292</v>
       </c>
       <c r="V2" t="n">
         <v>1.8358</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. LAPASTORA ARACIL</t>
+          <t>L. GARCIA LARRACHE SEGURA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.2066</v>
+        <v>1.5599</v>
       </c>
       <c r="E3" t="n">
-        <v>5.1469</v>
+        <v>2.6771</v>
       </c>
       <c r="F3" t="n">
-        <v>-2.9403</v>
+        <v>-1.1171</v>
       </c>
       <c r="G3" t="n">
-        <v>-1.0534</v>
+        <v>3.599</v>
       </c>
       <c r="H3" t="n">
-        <v>-1.0768</v>
+        <v>2.2821</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0234</v>
+        <v>1.3169</v>
       </c>
       <c r="J3" t="n">
-        <v>2.2316</v>
+        <v>6.1877</v>
       </c>
       <c r="K3" t="n">
-        <v>0.9681</v>
+        <v>2.9577</v>
       </c>
       <c r="L3" t="n">
-        <v>1.2635</v>
+        <v>3.23</v>
       </c>
       <c r="M3" t="n">
-        <v>-3.2851</v>
+        <v>-2.5887</v>
       </c>
       <c r="N3" t="n">
-        <v>-2.0449</v>
+        <v>-0.6756</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.2402</v>
+        <v>-1.9131</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.3881</v>
+        <v>-3.1045</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.9403</v>
+        <v>-4.8508</v>
       </c>
       <c r="R3" t="n">
-        <v>1.5523</v>
+        <v>1.7463</v>
       </c>
       <c r="S3" t="n">
-        <v>1.578</v>
+        <v>-0.4405</v>
       </c>
       <c r="T3" t="n">
-        <v>2.1736</v>
+        <v>-0.1657</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.5955</v>
+        <v>-0.2748</v>
       </c>
       <c r="V3" t="n">
-        <v>2.0701</v>
+        <v>1.506</v>
       </c>
       <c r="W3" t="n">
-        <v>2.6821</v>
+        <v>1.506</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.6119</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>L. GARCIA LARRACHE SEGURA</t>
+          <t>D. MANZANERO CAMACHO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.6234</v>
+        <v>1.0012</v>
       </c>
       <c r="E4" t="n">
-        <v>2.577</v>
+        <v>2.5247</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.9536</v>
+        <v>-1.5235</v>
       </c>
       <c r="G4" t="n">
-        <v>3.599</v>
+        <v>-0.6831</v>
       </c>
       <c r="H4" t="n">
-        <v>2.2821</v>
+        <v>-0.7415</v>
       </c>
       <c r="I4" t="n">
-        <v>1.3169</v>
+        <v>0.0584</v>
       </c>
       <c r="J4" t="n">
-        <v>6.1877</v>
+        <v>2.3848</v>
       </c>
       <c r="K4" t="n">
-        <v>2.9577</v>
+        <v>1.6313</v>
       </c>
       <c r="L4" t="n">
-        <v>3.23</v>
+        <v>0.7536</v>
       </c>
       <c r="M4" t="n">
-        <v>-2.5887</v>
+        <v>-3.0679</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.6756</v>
+        <v>-2.3728</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.9131</v>
+        <v>-0.6952</v>
       </c>
       <c r="P4" t="n">
-        <v>-3.1045</v>
+        <v>0.194</v>
       </c>
       <c r="Q4" t="n">
-        <v>-4.8508</v>
+        <v>-0.9702</v>
       </c>
       <c r="R4" t="n">
-        <v>1.7463</v>
+        <v>1.1642</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.3771</v>
+        <v>0.2664</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.2658</v>
+        <v>-0.1139</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.1112</v>
+        <v>0.3802</v>
       </c>
       <c r="V4" t="n">
-        <v>1.506</v>
+        <v>1.2239</v>
       </c>
       <c r="W4" t="n">
-        <v>1.506</v>
+        <v>1.2239</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>D. MANZANERO CAMACHO</t>
+          <t>J. LAPASTORA ARACIL</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.4006</v>
+        <v>0.8776</v>
       </c>
       <c r="E5" t="n">
-        <v>2.3245</v>
+        <v>3.5453</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.9239000000000001</v>
+        <v>-2.6677</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.6831</v>
+        <v>-1.0534</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.7415</v>
+        <v>-1.0768</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0584</v>
+        <v>0.0234</v>
       </c>
       <c r="J5" t="n">
-        <v>2.3848</v>
+        <v>2.2316</v>
       </c>
       <c r="K5" t="n">
-        <v>1.6313</v>
+        <v>0.9681</v>
       </c>
       <c r="L5" t="n">
-        <v>0.7536</v>
+        <v>1.2635</v>
       </c>
       <c r="M5" t="n">
-        <v>-3.0679</v>
+        <v>-3.2851</v>
       </c>
       <c r="N5" t="n">
-        <v>-2.3728</v>
+        <v>-2.0449</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.6952</v>
+        <v>-1.2402</v>
       </c>
       <c r="P5" t="n">
-        <v>0.194</v>
+        <v>-0.3881</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.9702</v>
+        <v>-1.9403</v>
       </c>
       <c r="R5" t="n">
-        <v>1.1642</v>
+        <v>1.5523</v>
       </c>
       <c r="S5" t="n">
-        <v>0.6657999999999999</v>
+        <v>0.249</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.3141</v>
+        <v>0.572</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9798</v>
+        <v>-0.323</v>
       </c>
       <c r="V5" t="n">
-        <v>1.2239</v>
+        <v>2.0701</v>
       </c>
       <c r="W5" t="n">
-        <v>1.2239</v>
+        <v>2.6821</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-0.6119</v>
       </c>
     </row>
     <row r="6">
@@ -877,10 +877,10 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.3606</v>
+        <v>-0.2605</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.3248</v>
+        <v>-0.2247</v>
       </c>
       <c r="F6" t="n">
         <v>-0.0358</v>
@@ -922,10 +922,10 @@
         <v>0.3881</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0123</v>
+        <v>0.1124</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.0482</v>
+        <v>0.0519</v>
       </c>
       <c r="U6" t="n">
         <v>0.0606</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.4165</v>
+        <v>-0.7441</v>
       </c>
       <c r="E7" t="n">
-        <v>2.1311</v>
+        <v>1.8308</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.5477</v>
+        <v>-2.5749</v>
       </c>
       <c r="G7" t="n">
         <v>-0.9076</v>
@@ -1000,13 +1000,13 @@
         <v>1.7463</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.2851</v>
+        <v>-0.6127</v>
       </c>
       <c r="T7" t="n">
-        <v>0.3409</v>
+        <v>0.0406</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.626</v>
+        <v>-0.6533</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.1247</v>
+        <v>-0.7521</v>
       </c>
       <c r="E8" t="n">
-        <v>1.1356</v>
+        <v>1.2357</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.2603</v>
+        <v>-1.9878</v>
       </c>
       <c r="G8" t="n">
         <v>-0.3968</v>
@@ -1078,13 +1078,13 @@
         <v>1.5523</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.31</v>
+        <v>-0.9373</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.3511</v>
+        <v>-0.251</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.9589</v>
+        <v>-0.6864</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. HERMOSO ALCUBILLA</t>
+          <t>E. MARTINEZ ALVAREZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.0986</v>
+        <v>-1.8807</v>
       </c>
       <c r="E9" t="n">
-        <v>0.521</v>
+        <v>-0.8804999999999999</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.6196</v>
+        <v>-1.0002</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.397</v>
+        <v>-1.4503</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.3882</v>
+        <v>-0.4054</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.0088</v>
+        <v>-1.0449</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.5326</v>
+        <v>0.3098</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.6138</v>
+        <v>1.071</v>
       </c>
       <c r="L9" t="n">
-        <v>0.08119999999999999</v>
+        <v>-0.7613</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.8645</v>
+        <v>-1.76</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.7744</v>
+        <v>-1.4764</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.09</v>
+        <v>-0.2836</v>
       </c>
       <c r="P9" t="n">
-        <v>0.194</v>
+        <v>-0.194</v>
       </c>
       <c r="Q9" t="n">
         <v>-0.9702</v>
       </c>
       <c r="R9" t="n">
-        <v>1.1642</v>
+        <v>0.7761</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.8374</v>
+        <v>0.0457</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.424</v>
+        <v>-0.2201</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.4134</v>
+        <v>0.2658</v>
       </c>
       <c r="V9" t="n">
-        <v>0.9418</v>
+        <v>-0.2821</v>
       </c>
       <c r="W9" t="n">
-        <v>2.4477</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.506</v>
+        <v>-0.2821</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>E. MARTINEZ ALVAREZ</t>
+          <t>M. HERMOSO ALCUBILLA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.399</v>
+        <v>-2.2165</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.1808</v>
+        <v>0.6211</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.2182</v>
+        <v>-2.8376</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.4503</v>
+        <v>-2.397</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.4054</v>
+        <v>-1.3882</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.0449</v>
+        <v>-1.0088</v>
       </c>
       <c r="J10" t="n">
-        <v>0.3098</v>
+        <v>-0.5326</v>
       </c>
       <c r="K10" t="n">
-        <v>1.071</v>
+        <v>-0.6138</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.7613</v>
+        <v>0.08119999999999999</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.76</v>
+        <v>-1.8645</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.4764</v>
+        <v>-0.7744</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.2836</v>
+        <v>-1.09</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.194</v>
+        <v>0.194</v>
       </c>
       <c r="Q10" t="n">
         <v>-0.9702</v>
       </c>
       <c r="R10" t="n">
-        <v>0.7761</v>
+        <v>1.1642</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.4726</v>
+        <v>-0.9553</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.5204</v>
+        <v>-0.3239</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0478</v>
+        <v>-0.6314</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.2821</v>
+        <v>0.9418</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>2.4477</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.2821</v>
+        <v>-1.506</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.3282</v>
+        <v>-3.8916</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.1312</v>
+        <v>-1.8309</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.197</v>
+        <v>-2.0607</v>
       </c>
       <c r="G11" t="n">
         <v>-4.7533</v>
@@ -1312,13 +1312,13 @@
         <v>0.5821</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.7212</v>
+        <v>-0.2846</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.581</v>
+        <v>-0.2807</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1402</v>
+        <v>-0.0039</v>
       </c>
       <c r="V11" t="n">
         <v>0.5642</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.8479</v>
+        <v>-4.3112</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.0449</v>
+        <v>-2.6445</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.803</v>
+        <v>-1.6667</v>
       </c>
       <c r="G12" t="n">
         <v>-3.451</v>
@@ -1390,13 +1390,13 @@
         <v>0.7761</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.5148</v>
+        <v>0.0219</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.5081</v>
+        <v>-0.1077</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.0067</v>
+        <v>0.1296</v>
       </c>
       <c r="V12" t="n">
         <v>0.2821</v>
@@ -1429,7 +1429,7 @@
         <v>11.6892</v>
       </c>
       <c r="F13" t="n">
-        <v>-19.5113</v>
+        <v>-19.5111</v>
       </c>
       <c r="G13" t="n">
         <v>-12.6887</v>
@@ -1438,7 +1438,7 @@
         <v>-5.932000000000001</v>
       </c>
       <c r="I13" t="n">
-        <v>-6.756599999999999</v>
+        <v>-6.756600000000001</v>
       </c>
       <c r="J13" t="n">
         <v>14.4511</v>
@@ -1468,13 +1468,13 @@
         <v>12.6122</v>
       </c>
       <c r="S13" t="n">
-        <v>-2.3049</v>
+        <v>-2.304800000000001</v>
       </c>
       <c r="T13" t="n">
         <v>-0.8975000000000001</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.4072</v>
+        <v>-1.4074</v>
       </c>
       <c r="V13" t="n">
         <v>8.1418</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>7.7978</v>
+        <v>8.0398</v>
       </c>
       <c r="E14" t="n">
-        <v>8.216900000000001</v>
+        <v>7.5163</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.4192</v>
+        <v>0.5235</v>
       </c>
       <c r="G14" t="n">
         <v>5.0376</v>
@@ -1546,13 +1546,13 @@
         <v>2.3284</v>
       </c>
       <c r="S14" t="n">
-        <v>0.4318</v>
+        <v>0.6738</v>
       </c>
       <c r="T14" t="n">
-        <v>1.0576</v>
+        <v>0.3569</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.6258</v>
+        <v>0.3169</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>F. DIAZ ZARZUELA</t>
+          <t>B. OJEDA OCHOA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>5.8797</v>
+        <v>6.4383</v>
       </c>
       <c r="E15" t="n">
-        <v>4.8218</v>
+        <v>6.8555</v>
       </c>
       <c r="F15" t="n">
-        <v>1.0579</v>
+        <v>-0.4172</v>
       </c>
       <c r="G15" t="n">
-        <v>4.3576</v>
+        <v>4.896</v>
       </c>
       <c r="H15" t="n">
-        <v>3.3243</v>
+        <v>1.1205</v>
       </c>
       <c r="I15" t="n">
-        <v>1.0332</v>
+        <v>3.7755</v>
       </c>
       <c r="J15" t="n">
-        <v>5.0989</v>
+        <v>6.3162</v>
       </c>
       <c r="K15" t="n">
-        <v>3.6374</v>
+        <v>1.8455</v>
       </c>
       <c r="L15" t="n">
-        <v>1.4615</v>
+        <v>4.4707</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.7413</v>
+        <v>-1.4202</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.3131</v>
+        <v>-0.725</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.4282</v>
+        <v>-0.6952</v>
       </c>
       <c r="P15" t="n">
-        <v>0.9702</v>
+        <v>-0.194</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.9702</v>
+        <v>-1.9403</v>
       </c>
       <c r="R15" t="n">
-        <v>1.9403</v>
+        <v>1.7463</v>
       </c>
       <c r="S15" t="n">
-        <v>0.552</v>
+        <v>0.7946</v>
       </c>
       <c r="T15" t="n">
-        <v>0.6931</v>
+        <v>0.0319</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.1411</v>
+        <v>0.7627</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>0.9418</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>2.4477</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-1.506</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>B. OJEDA OCHOA</t>
+          <t>F. DIAZ ZARZUELA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>5.4129</v>
+        <v>5.8403</v>
       </c>
       <c r="E16" t="n">
-        <v>6.2549</v>
+        <v>4.2212</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.842</v>
+        <v>1.619</v>
       </c>
       <c r="G16" t="n">
-        <v>4.896</v>
+        <v>4.3576</v>
       </c>
       <c r="H16" t="n">
-        <v>1.1205</v>
+        <v>3.3243</v>
       </c>
       <c r="I16" t="n">
-        <v>3.7755</v>
+        <v>1.0332</v>
       </c>
       <c r="J16" t="n">
-        <v>6.3162</v>
+        <v>5.0989</v>
       </c>
       <c r="K16" t="n">
-        <v>1.8455</v>
+        <v>3.6374</v>
       </c>
       <c r="L16" t="n">
-        <v>4.4707</v>
+        <v>1.4615</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.4202</v>
+        <v>-0.7413</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.725</v>
+        <v>-0.3131</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.6952</v>
+        <v>-0.4282</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.194</v>
+        <v>0.9702</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.9403</v>
+        <v>-0.9702</v>
       </c>
       <c r="R16" t="n">
-        <v>1.7463</v>
+        <v>1.9403</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.2308</v>
+        <v>0.5125999999999999</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.5687</v>
+        <v>0.0925</v>
       </c>
       <c r="U16" t="n">
-        <v>0.3378</v>
+        <v>0.4201</v>
       </c>
       <c r="V16" t="n">
-        <v>0.9418</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>2.4477</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.506</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.243</v>
+        <v>2.6767</v>
       </c>
       <c r="E17" t="n">
-        <v>3.0958</v>
+        <v>3.3961</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.8528</v>
+        <v>-0.7194</v>
       </c>
       <c r="G17" t="n">
         <v>2.7063</v>
@@ -1780,13 +1780,13 @@
         <v>0.9702</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.1335</v>
+        <v>0.3003</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.1694</v>
+        <v>0.1309</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0359</v>
+        <v>0.1694</v>
       </c>
       <c r="V17" t="n">
         <v>-0.3299</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.5083</v>
+        <v>2.3152</v>
       </c>
       <c r="E18" t="n">
-        <v>3.3312</v>
+        <v>3.6315</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.8229</v>
+        <v>-1.3163</v>
       </c>
       <c r="G18" t="n">
         <v>-0.0111</v>
@@ -1858,13 +1858,13 @@
         <v>1.7463</v>
       </c>
       <c r="S18" t="n">
-        <v>0.103</v>
+        <v>0.9099</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.1559</v>
+        <v>0.1444</v>
       </c>
       <c r="U18" t="n">
-        <v>0.2589</v>
+        <v>0.7655</v>
       </c>
       <c r="V18" t="n">
         <v>-0.3299</v>
@@ -1891,10 +1891,10 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.4389</v>
+        <v>-0.8393</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.221</v>
+        <v>-0.6214</v>
       </c>
       <c r="F19" t="n">
         <v>-0.2179</v>
@@ -1936,10 +1936,10 @@
         <v>0.194</v>
       </c>
       <c r="S19" t="n">
-        <v>0.6673</v>
+        <v>0.2669</v>
       </c>
       <c r="T19" t="n">
-        <v>0.6673</v>
+        <v>0.2669</v>
       </c>
       <c r="U19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.3438</v>
+        <v>-1.6131</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.2403</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.1036</v>
+        <v>-0.6731</v>
       </c>
       <c r="G20" t="n">
         <v>-1.1409</v>
@@ -2014,13 +2014,13 @@
         <v>0.7761</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.4731</v>
+        <v>0.2577</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.4845</v>
+        <v>-0.1842</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0115</v>
+        <v>0.4419</v>
       </c>
       <c r="V20" t="n">
         <v>-1.506</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.4158</v>
+        <v>-3.1578</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.1087</v>
+        <v>-1.0086</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.3071</v>
+        <v>-2.1492</v>
       </c>
       <c r="G21" t="n">
         <v>1.4393</v>
@@ -2092,13 +2092,13 @@
         <v>0.5821</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.4372</v>
+        <v>-0.1792</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.3028</v>
+        <v>-0.2027</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.1343</v>
+        <v>0.0236</v>
       </c>
       <c r="V21" t="n">
         <v>-3.0597</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.2305</v>
+        <v>-3.7878</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.8696</v>
+        <v>-0.6694</v>
       </c>
       <c r="F22" t="n">
-        <v>-3.3609</v>
+        <v>-3.1184</v>
       </c>
       <c r="G22" t="n">
         <v>-1.7211</v>
@@ -2170,13 +2170,13 @@
         <v>1.5523</v>
       </c>
       <c r="S22" t="n">
-        <v>0.2308</v>
+        <v>0.6735</v>
       </c>
       <c r="T22" t="n">
-        <v>0.0863</v>
+        <v>0.2865</v>
       </c>
       <c r="U22" t="n">
-        <v>0.1445</v>
+        <v>0.387</v>
       </c>
       <c r="V22" t="n">
         <v>-2.3522</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.5905</v>
+        <v>-4.7536</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.7698</v>
+        <v>-2.8699</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.8207</v>
+        <v>-1.8836</v>
       </c>
       <c r="G23" t="n">
         <v>-2.5446</v>
@@ -2248,13 +2248,13 @@
         <v>1.7463</v>
       </c>
       <c r="S23" t="n">
-        <v>1.5944</v>
+        <v>1.4314</v>
       </c>
       <c r="T23" t="n">
-        <v>0.5843</v>
+        <v>0.4842</v>
       </c>
       <c r="U23" t="n">
-        <v>1.0101</v>
+        <v>0.9472</v>
       </c>
       <c r="V23" t="n">
         <v>-1.506</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>7.822199999999998</v>
+        <v>11.1587</v>
       </c>
       <c r="E24" t="n">
-        <v>19.5112</v>
+        <v>19.5113</v>
       </c>
       <c r="F24" t="n">
-        <v>-11.6892</v>
+        <v>-8.352600000000001</v>
       </c>
       <c r="G24" t="n">
         <v>12.689</v>
@@ -2326,13 +2326,13 @@
         <v>13.5823</v>
       </c>
       <c r="S24" t="n">
-        <v>2.3047</v>
+        <v>5.6415</v>
       </c>
       <c r="T24" t="n">
         <v>1.4073</v>
       </c>
       <c r="U24" t="n">
-        <v>0.8975</v>
+        <v>4.2343</v>
       </c>
       <c r="V24" t="n">
         <v>-8.1419</v>
